--- a/concentration_calculation/species_concentration_output.xlsx
+++ b/concentration_calculation/species_concentration_output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,7 +484,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -495,7 +495,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2.295615041681997</v>
+        <v>2.161787568220504</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -517,11 +517,11 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ATP</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.05583598045277717</v>
+        <v>4.323575136441009</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -558,7 +558,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ATM</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.6095662772098134</v>
+        <v>0.07854846717525865</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -588,25 +588,25 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.6308292302412286</v>
+        <v>0.07854846717525865</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -643,7 +643,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.295615267817837</v>
+        <v>2.240336035395761</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -669,18 +669,18 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ATP</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ER</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -689,83 +689,9 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.05583603924809548</v>
+        <v>1.759663964604238</v>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>MET</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0.6096826654722615</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ADP</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0.6308288887761108</v>
-      </c>
-      <c r="I9" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
